--- a/codigo/firmware/Controlador/Prototipo/pines.xlsx
+++ b/codigo/firmware/Controlador/Prototipo/pines.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -67,9 +67,6 @@
     <t>PB11</t>
   </si>
   <si>
-    <t>GORUND</t>
-  </si>
-  <si>
     <t>PB2</t>
   </si>
   <si>
@@ -308,6 +305,9 @@
   </si>
   <si>
     <t>Medición</t>
+  </si>
+  <si>
+    <t>GRoUND</t>
   </si>
 </sst>
 </file>
@@ -881,7 +881,7 @@
   <sheetData>
     <row r="1" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B1" s="44" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C1" s="44"/>
       <c r="D1" s="44"/>
@@ -898,10 +898,10 @@
         <v>1</v>
       </c>
       <c r="C2" s="26" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D2" s="27" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E2">
         <v>2</v>
@@ -924,10 +924,10 @@
         <v>3</v>
       </c>
       <c r="C3" s="28" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D3" s="29" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E3">
         <v>4</v>
@@ -950,10 +950,10 @@
         <v>5</v>
       </c>
       <c r="C4" s="28" t="s">
+        <v>36</v>
+      </c>
+      <c r="D4" s="29" t="s">
         <v>37</v>
-      </c>
-      <c r="D4" s="29" t="s">
-        <v>38</v>
       </c>
       <c r="E4">
         <v>6</v>
@@ -976,7 +976,7 @@
         <v>7</v>
       </c>
       <c r="C5" s="28" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D5" s="29" t="s">
         <v>4</v>
@@ -1002,7 +1002,7 @@
         <v>9</v>
       </c>
       <c r="C6" s="28" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D6" s="29"/>
       <c r="E6">
@@ -1029,7 +1029,7 @@
         <v>11</v>
       </c>
       <c r="C7" s="28" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D7" s="29"/>
       <c r="E7">
@@ -1042,7 +1042,7 @@
         <v>11</v>
       </c>
       <c r="I7" s="34" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J7" s="17" t="s">
         <v>13</v>
@@ -1056,10 +1056,10 @@
         <v>13</v>
       </c>
       <c r="C8" s="28" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D8" s="29" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E8">
         <v>14</v>
@@ -1071,7 +1071,7 @@
         <v>13</v>
       </c>
       <c r="I8" s="34" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J8" s="17" t="s">
         <v>14</v>
@@ -1085,10 +1085,10 @@
         <v>15</v>
       </c>
       <c r="C9" s="28" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D9" s="29" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E9">
         <v>16</v>
@@ -1100,7 +1100,7 @@
         <v>15</v>
       </c>
       <c r="I9" s="34" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J9" s="19" t="s">
         <v>15</v>
@@ -1114,7 +1114,7 @@
         <v>17</v>
       </c>
       <c r="C10" s="28" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D10" s="29"/>
       <c r="E10">
@@ -1157,7 +1157,7 @@
         <v>11</v>
       </c>
       <c r="J11" s="17" t="s">
-        <v>17</v>
+        <v>97</v>
       </c>
       <c r="K11">
         <v>20</v>
@@ -1168,7 +1168,7 @@
         <v>21</v>
       </c>
       <c r="C12" s="33" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D12" s="29"/>
       <c r="E12">
@@ -1184,7 +1184,7 @@
         <v>12</v>
       </c>
       <c r="J12" s="17" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="K12">
         <v>22</v>
@@ -1195,7 +1195,7 @@
         <v>23</v>
       </c>
       <c r="C13" s="28" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D13" s="29"/>
       <c r="E13">
@@ -1208,10 +1208,10 @@
         <v>23</v>
       </c>
       <c r="I13" s="18" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J13" s="20" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="K13">
         <v>24</v>
@@ -1222,7 +1222,7 @@
         <v>25</v>
       </c>
       <c r="C14" s="28" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D14" s="29"/>
       <c r="E14">
@@ -1232,7 +1232,7 @@
         <v>25</v>
       </c>
       <c r="I14" s="16" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="J14" s="29"/>
       <c r="K14">
@@ -1244,10 +1244,10 @@
         <v>27</v>
       </c>
       <c r="C15" s="28" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D15" s="30" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E15">
         <v>28</v>
@@ -1259,7 +1259,7 @@
         <v>27</v>
       </c>
       <c r="I15" s="21" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J15" s="29"/>
       <c r="K15">
@@ -1271,10 +1271,10 @@
         <v>29</v>
       </c>
       <c r="C16" s="28" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D16" s="30" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E16">
         <v>30</v>
@@ -1286,7 +1286,7 @@
         <v>29</v>
       </c>
       <c r="I16" s="22" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="J16" s="29"/>
       <c r="K16">
@@ -1298,10 +1298,10 @@
         <v>31</v>
       </c>
       <c r="C17" s="28" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D17" s="30" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E17">
         <v>32</v>
@@ -1313,7 +1313,7 @@
         <v>31</v>
       </c>
       <c r="I17" s="21" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J17" s="17"/>
       <c r="K17">
@@ -1325,10 +1325,10 @@
         <v>33</v>
       </c>
       <c r="C18" s="28" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D18" s="30" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E18">
         <v>34</v>
@@ -1340,10 +1340,10 @@
         <v>33</v>
       </c>
       <c r="I18" s="35" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="J18" s="17" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="K18">
         <v>34</v>
@@ -1354,10 +1354,10 @@
         <v>35</v>
       </c>
       <c r="C19" s="28" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D19" s="30" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E19">
         <v>36</v>
@@ -1369,10 +1369,10 @@
         <v>35</v>
       </c>
       <c r="I19" s="23" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="J19" s="17" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="K19">
         <v>36</v>
@@ -1383,10 +1383,10 @@
         <v>37</v>
       </c>
       <c r="C20" s="31" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D20" s="32" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E20">
         <v>38</v>
@@ -1398,10 +1398,10 @@
         <v>37</v>
       </c>
       <c r="I20" s="24" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="J20" s="25" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="K20">
         <v>38</v>
@@ -1410,25 +1410,25 @@
     <row r="23" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C23" s="1"/>
       <c r="D23" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C24" s="2"/>
       <c r="D24" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C25" s="3"/>
       <c r="D25" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C26" s="4"/>
       <c r="D26" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.25">
@@ -1437,93 +1437,93 @@
     <row r="28" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="29" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A29" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="B29" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="B29" s="6" t="s">
+      <c r="C29" s="7" t="s">
         <v>68</v>
-      </c>
-      <c r="C29" s="7" t="s">
-        <v>69</v>
       </c>
       <c r="F29" s="36"/>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A30" s="8" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B30" s="9" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C30" s="10" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F30" s="42" t="s">
+        <v>95</v>
+      </c>
+      <c r="G30" s="43" t="s">
         <v>96</v>
-      </c>
-      <c r="G30" s="43" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A31" s="8" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B31" s="9" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C31" s="10" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F31" s="38" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G31" s="40" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="32" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A32" s="11" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B32" s="12" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C32" s="13" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F32" s="38" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="G32" s="40" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="33" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="F33" s="38" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G33" s="40" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A34" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="B34" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="C34" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="B34" s="6" t="s">
-        <v>75</v>
-      </c>
-      <c r="C34" s="6" t="s">
+      <c r="D34" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="D34" s="7" t="s">
-        <v>69</v>
-      </c>
       <c r="F34" s="38" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="G34" s="40" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.25">
@@ -1534,16 +1534,16 @@
         <v>1</v>
       </c>
       <c r="C35" s="9" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D35" s="10" t="s">
         <v>10</v>
       </c>
       <c r="F35" s="38" t="s">
+        <v>88</v>
+      </c>
+      <c r="G35" s="40" t="s">
         <v>89</v>
-      </c>
-      <c r="G35" s="40" t="s">
-        <v>90</v>
       </c>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.25">
@@ -1554,16 +1554,16 @@
         <v>2</v>
       </c>
       <c r="C36" s="9" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D36" s="10" t="s">
-        <v>53</v>
+        <v>15</v>
       </c>
       <c r="F36" s="38" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="G36" s="40" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.25">
@@ -1574,16 +1574,16 @@
         <v>1</v>
       </c>
       <c r="C37" s="9" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D37" s="10" t="s">
         <v>1</v>
       </c>
       <c r="F37" s="38" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G37" s="40" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.25">
@@ -1594,16 +1594,16 @@
         <v>2</v>
       </c>
       <c r="C38" s="9" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D38" s="10" t="s">
         <v>2</v>
       </c>
       <c r="F38" s="38" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G38" s="40" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.25">
@@ -1614,16 +1614,16 @@
         <v>1</v>
       </c>
       <c r="C39" s="9" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D39" s="10" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F39" s="38" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G39" s="40" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="40" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -1634,16 +1634,16 @@
         <v>2</v>
       </c>
       <c r="C40" s="12" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D40" s="13" t="s">
         <v>16</v>
       </c>
       <c r="F40" s="39" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G40" s="41" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="I40" s="37"/>
     </row>

--- a/codigo/firmware/Controlador/Prototipo/pines.xlsx
+++ b/codigo/firmware/Controlador/Prototipo/pines.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010"/>
+    <workbookView minimized="1" xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="109">
   <si>
     <t>PC9</t>
   </si>
@@ -308,6 +308,39 @@
   </si>
   <si>
     <t>GRoUND</t>
+  </si>
+  <si>
+    <t>IN0</t>
+  </si>
+  <si>
+    <t>IN4</t>
+  </si>
+  <si>
+    <t>IN5</t>
+  </si>
+  <si>
+    <t>IN6</t>
+  </si>
+  <si>
+    <t>IN7</t>
+  </si>
+  <si>
+    <t>IN8</t>
+  </si>
+  <si>
+    <t>IN10</t>
+  </si>
+  <si>
+    <t>IN11</t>
+  </si>
+  <si>
+    <t>IN14</t>
+  </si>
+  <si>
+    <t>CANAL ADC</t>
+  </si>
+  <si>
+    <t>IN1</t>
   </si>
 </sst>
 </file>
@@ -461,7 +494,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
@@ -563,11 +596,20 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -876,22 +918,23 @@
   <dimension ref="A1:K42"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
+    <col min="8" max="8" width="11.140625" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="9.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B1" s="44" t="s">
+      <c r="B1" s="43" t="s">
         <v>82</v>
       </c>
-      <c r="C1" s="44"/>
-      <c r="D1" s="44"/>
-      <c r="E1" s="44"/>
-      <c r="F1" s="44"/>
-      <c r="G1" s="44"/>
-      <c r="H1" s="44"/>
-      <c r="I1" s="44"/>
-      <c r="J1" s="44"/>
-      <c r="K1" s="44"/>
+      <c r="C1" s="43"/>
+      <c r="D1" s="43"/>
+      <c r="E1" s="43"/>
+      <c r="F1" s="43"/>
+      <c r="G1" s="43"/>
+      <c r="H1" s="43"/>
+      <c r="I1" s="43"/>
+      <c r="J1" s="43"/>
+      <c r="K1" s="43"/>
     </row>
     <row r="2" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B2">
@@ -1460,8 +1503,11 @@
       <c r="F30" s="42" t="s">
         <v>95</v>
       </c>
-      <c r="G30" s="43" t="s">
+      <c r="G30" s="45" t="s">
         <v>96</v>
+      </c>
+      <c r="H30" s="47" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.25">
@@ -1477,8 +1523,11 @@
       <c r="F31" s="38" t="s">
         <v>43</v>
       </c>
-      <c r="G31" s="40" t="s">
+      <c r="G31" s="44" t="s">
         <v>85</v>
+      </c>
+      <c r="H31" s="40" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="32" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -1494,16 +1543,22 @@
       <c r="F32" s="38" t="s">
         <v>44</v>
       </c>
-      <c r="G32" s="40" t="s">
+      <c r="G32" s="44" t="s">
         <v>86</v>
+      </c>
+      <c r="H32" s="40" t="s">
+        <v>108</v>
       </c>
     </row>
     <row r="33" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="F33" s="38" t="s">
         <v>45</v>
       </c>
-      <c r="G33" s="40" t="s">
+      <c r="G33" s="44" t="s">
         <v>83</v>
+      </c>
+      <c r="H33" s="40" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.25">
@@ -1522,8 +1577,11 @@
       <c r="F34" s="38" t="s">
         <v>46</v>
       </c>
-      <c r="G34" s="40" t="s">
+      <c r="G34" s="44" t="s">
         <v>87</v>
+      </c>
+      <c r="H34" s="40" t="s">
+        <v>103</v>
       </c>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.25">
@@ -1542,8 +1600,11 @@
       <c r="F35" s="38" t="s">
         <v>88</v>
       </c>
-      <c r="G35" s="40" t="s">
+      <c r="G35" s="44" t="s">
         <v>89</v>
+      </c>
+      <c r="H35" s="40" t="s">
+        <v>104</v>
       </c>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.25">
@@ -1562,8 +1623,11 @@
       <c r="F36" s="38" t="s">
         <v>91</v>
       </c>
-      <c r="G36" s="40" t="s">
+      <c r="G36" s="44" t="s">
         <v>90</v>
+      </c>
+      <c r="H36" s="40" t="s">
+        <v>105</v>
       </c>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.25">
@@ -1582,8 +1646,11 @@
       <c r="F37" s="38" t="s">
         <v>19</v>
       </c>
-      <c r="G37" s="40" t="s">
+      <c r="G37" s="44" t="s">
         <v>93</v>
+      </c>
+      <c r="H37" s="40" t="s">
+        <v>102</v>
       </c>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.25">
@@ -1602,8 +1669,11 @@
       <c r="F38" s="38" t="s">
         <v>20</v>
       </c>
-      <c r="G38" s="40" t="s">
+      <c r="G38" s="44" t="s">
         <v>92</v>
+      </c>
+      <c r="H38" s="40" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.25">
@@ -1622,8 +1692,11 @@
       <c r="F39" s="38" t="s">
         <v>21</v>
       </c>
-      <c r="G39" s="40" t="s">
+      <c r="G39" s="44" t="s">
         <v>84</v>
+      </c>
+      <c r="H39" s="40" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="40" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -1642,8 +1715,11 @@
       <c r="F40" s="39" t="s">
         <v>29</v>
       </c>
-      <c r="G40" s="41" t="s">
+      <c r="G40" s="46" t="s">
         <v>94</v>
+      </c>
+      <c r="H40" s="41" t="s">
+        <v>106</v>
       </c>
       <c r="I40" s="37"/>
     </row>

--- a/codigo/firmware/Controlador/Prototipo/pines.xlsx
+++ b/codigo/firmware/Controlador/Prototipo/pines.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="119">
   <si>
     <t>PC9</t>
   </si>
@@ -271,9 +271,6 @@
     <t>bus_1</t>
   </si>
   <si>
-    <t>cell_11</t>
-  </si>
-  <si>
     <t>cell_12</t>
   </si>
   <si>
@@ -316,15 +313,6 @@
     <t>IN4</t>
   </si>
   <si>
-    <t>IN5</t>
-  </si>
-  <si>
-    <t>IN6</t>
-  </si>
-  <si>
-    <t>IN7</t>
-  </si>
-  <si>
     <t>IN8</t>
   </si>
   <si>
@@ -341,13 +329,165 @@
   </si>
   <si>
     <t>IN1</t>
+  </si>
+  <si>
+    <t>x</t>
+  </si>
+  <si>
+    <t>IN12</t>
+  </si>
+  <si>
+    <t>IN13</t>
+  </si>
+  <si>
+    <r>
+      <t>ADC_NODE_CELL_12</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>ADC_NODE_CELL_21</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>ADC_NODE_CELL_22</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>ADC_NODE_CELL_31</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>ADC_NODE_CELL_32</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>ADC_NODE_OUT_NEG</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>ADC_NODE_BUS_1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>ADC_NODE_BUS_2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>ADC_NODE_OUT_POS</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+  </si>
+  <si>
+    <t>ADC_NODE_COUNT</t>
+  </si>
+  <si>
+    <r>
+      <t>ADC_NODE_CELL_11</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -368,6 +508,27 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="10"/>
+      <color rgb="FF0000C0"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <i/>
+      <u/>
+      <sz val="10"/>
+      <color rgb="FF0066CC"/>
+      <name val="Consolas"/>
+      <family val="3"/>
     </font>
   </fonts>
   <fills count="6">
@@ -402,7 +563,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -490,11 +651,48 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="48">
+  <cellXfs count="53">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
@@ -568,12 +766,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -593,23 +786,39 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -915,26 +1124,27 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K42"/>
+  <dimension ref="A1:O41"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="8" max="8" width="11.140625" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B1" s="43" t="s">
+      <c r="B1" s="41" t="s">
         <v>82</v>
       </c>
-      <c r="C1" s="43"/>
-      <c r="D1" s="43"/>
-      <c r="E1" s="43"/>
-      <c r="F1" s="43"/>
-      <c r="G1" s="43"/>
-      <c r="H1" s="43"/>
-      <c r="I1" s="43"/>
-      <c r="J1" s="43"/>
-      <c r="K1" s="43"/>
+      <c r="C1" s="41"/>
+      <c r="D1" s="41"/>
+      <c r="E1" s="41"/>
+      <c r="F1" s="41"/>
+      <c r="G1" s="41"/>
+      <c r="H1" s="41"/>
+      <c r="I1" s="41"/>
+      <c r="J1" s="41"/>
+      <c r="K1" s="41"/>
     </row>
     <row r="2" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B2">
@@ -1057,7 +1267,7 @@
       <c r="H6">
         <v>9</v>
       </c>
-      <c r="I6" s="18" t="s">
+      <c r="I6" s="32" t="s">
         <v>4</v>
       </c>
       <c r="J6" s="17" t="s">
@@ -1084,7 +1294,7 @@
       <c r="H7">
         <v>11</v>
       </c>
-      <c r="I7" s="34" t="s">
+      <c r="I7" s="32" t="s">
         <v>19</v>
       </c>
       <c r="J7" s="17" t="s">
@@ -1113,7 +1323,7 @@
       <c r="H8">
         <v>13</v>
       </c>
-      <c r="I8" s="34" t="s">
+      <c r="I8" s="32" t="s">
         <v>20</v>
       </c>
       <c r="J8" s="17" t="s">
@@ -1142,7 +1352,7 @@
       <c r="H9">
         <v>15</v>
       </c>
-      <c r="I9" s="34" t="s">
+      <c r="I9" s="32" t="s">
         <v>21</v>
       </c>
       <c r="J9" s="19" t="s">
@@ -1196,11 +1406,11 @@
       <c r="H11">
         <v>19</v>
       </c>
-      <c r="I11" s="18" t="s">
+      <c r="I11" s="32" t="s">
         <v>11</v>
       </c>
       <c r="J11" s="17" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="K11">
         <v>20</v>
@@ -1210,7 +1420,7 @@
       <c r="B12">
         <v>21</v>
       </c>
-      <c r="C12" s="33" t="s">
+      <c r="C12" s="31" t="s">
         <v>52</v>
       </c>
       <c r="D12" s="29"/>
@@ -1223,7 +1433,7 @@
       <c r="H12">
         <v>21</v>
       </c>
-      <c r="I12" s="34" t="s">
+      <c r="I12" s="32" t="s">
         <v>12</v>
       </c>
       <c r="J12" s="17" t="s">
@@ -1240,7 +1450,7 @@
       <c r="C13" s="28" t="s">
         <v>53</v>
       </c>
-      <c r="D13" s="29"/>
+      <c r="D13" s="50"/>
       <c r="E13">
         <v>24</v>
       </c>
@@ -1250,7 +1460,7 @@
       <c r="H13">
         <v>23</v>
       </c>
-      <c r="I13" s="18" t="s">
+      <c r="I13" s="32" t="s">
         <v>22</v>
       </c>
       <c r="J13" s="20" t="s">
@@ -1267,7 +1477,7 @@
       <c r="C14" s="28" t="s">
         <v>54</v>
       </c>
-      <c r="D14" s="29"/>
+      <c r="D14" s="50"/>
       <c r="E14">
         <v>26</v>
       </c>
@@ -1336,7 +1546,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B17">
         <v>31</v>
       </c>
@@ -1363,7 +1573,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B18">
         <v>33</v>
       </c>
@@ -1382,24 +1592,24 @@
       <c r="H18">
         <v>33</v>
       </c>
-      <c r="I18" s="35" t="s">
+      <c r="I18" s="32" t="s">
         <v>26</v>
       </c>
-      <c r="J18" s="17" t="s">
+      <c r="J18" s="52" t="s">
         <v>29</v>
       </c>
       <c r="K18">
         <v>34</v>
       </c>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B19">
         <v>35</v>
       </c>
-      <c r="C19" s="28" t="s">
+      <c r="C19" s="48" t="s">
         <v>58</v>
       </c>
-      <c r="D19" s="30" t="s">
+      <c r="D19" s="50" t="s">
         <v>47</v>
       </c>
       <c r="E19">
@@ -1421,14 +1631,14 @@
         <v>36</v>
       </c>
     </row>
-    <row r="20" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B20">
         <v>37</v>
       </c>
-      <c r="C20" s="31" t="s">
+      <c r="C20" s="49" t="s">
         <v>59</v>
       </c>
-      <c r="D20" s="32" t="s">
+      <c r="D20" s="51" t="s">
         <v>48</v>
       </c>
       <c r="E20">
@@ -1450,35 +1660,35 @@
         <v>38</v>
       </c>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
       <c r="C23" s="1"/>
       <c r="D23" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
       <c r="C24" s="2"/>
       <c r="D24" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="C25" s="3"/>
       <c r="D25" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
       <c r="C26" s="4"/>
       <c r="D26" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="I27" s="36"/>
-    </row>
-    <row r="28" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="29" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="I27" s="33"/>
+    </row>
+    <row r="28" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="29" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A29" s="5" t="s">
         <v>66</v>
       </c>
@@ -1488,9 +1698,9 @@
       <c r="C29" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="F29" s="36"/>
-    </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="F29" s="33"/>
+    </row>
+    <row r="30" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A30" s="8" t="s">
         <v>70</v>
       </c>
@@ -1500,17 +1710,20 @@
       <c r="C30" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="F30" s="42" t="s">
+      <c r="I30" s="45" t="s">
+        <v>94</v>
+      </c>
+      <c r="J30" s="46" t="s">
         <v>95</v>
       </c>
-      <c r="G30" s="45" t="s">
-        <v>96</v>
-      </c>
-      <c r="H30" s="47" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="K30" s="47" t="s">
+        <v>103</v>
+      </c>
+      <c r="O30" s="43" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="31" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A31" s="8" t="s">
         <v>72</v>
       </c>
@@ -1520,17 +1733,20 @@
       <c r="C31" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="F31" s="38" t="s">
-        <v>43</v>
-      </c>
-      <c r="G31" s="44" t="s">
+      <c r="I31" s="35" t="s">
+        <v>44</v>
+      </c>
+      <c r="J31" s="39" t="s">
         <v>85</v>
       </c>
-      <c r="H31" s="40" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="32" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K31" s="37" t="s">
+        <v>104</v>
+      </c>
+      <c r="O31" s="43" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="32" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A32" s="11" t="s">
         <v>81</v>
       </c>
@@ -1540,28 +1756,34 @@
       <c r="C32" s="13" t="s">
         <v>63</v>
       </c>
-      <c r="F32" s="38" t="s">
-        <v>44</v>
-      </c>
-      <c r="G32" s="44" t="s">
+      <c r="I32" s="35" t="s">
+        <v>45</v>
+      </c>
+      <c r="J32" s="39" t="s">
+        <v>83</v>
+      </c>
+      <c r="K32" s="37" t="s">
+        <v>98</v>
+      </c>
+      <c r="O32" s="43" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="33" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I33" s="35" t="s">
+        <v>46</v>
+      </c>
+      <c r="J33" s="39" t="s">
         <v>86</v>
       </c>
-      <c r="H32" s="40" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="33" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="F33" s="38" t="s">
-        <v>45</v>
-      </c>
-      <c r="G33" s="44" t="s">
-        <v>83</v>
-      </c>
-      <c r="H33" s="40" t="s">
+      <c r="K33" s="37" t="s">
         <v>99</v>
       </c>
-    </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="O33" s="43" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="34" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A34" s="5" t="s">
         <v>66</v>
       </c>
@@ -1574,17 +1796,20 @@
       <c r="D34" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="F34" s="38" t="s">
-        <v>46</v>
-      </c>
-      <c r="G34" s="44" t="s">
+      <c r="I34" s="35" t="s">
         <v>87</v>
       </c>
-      <c r="H34" s="40" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J34" s="39" t="s">
+        <v>88</v>
+      </c>
+      <c r="K34" s="37" t="s">
+        <v>100</v>
+      </c>
+      <c r="O34" s="43" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="35" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A35" s="8">
         <v>1</v>
       </c>
@@ -1597,17 +1822,20 @@
       <c r="D35" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="F35" s="38" t="s">
-        <v>88</v>
-      </c>
-      <c r="G35" s="44" t="s">
+      <c r="I35" s="35" t="s">
+        <v>90</v>
+      </c>
+      <c r="J35" s="39" t="s">
         <v>89</v>
       </c>
-      <c r="H35" s="40" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="K35" s="37" t="s">
+        <v>101</v>
+      </c>
+      <c r="O35" s="43" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="36" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A36" s="8">
         <v>1</v>
       </c>
@@ -1620,17 +1848,23 @@
       <c r="D36" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="F36" s="38" t="s">
+      <c r="I36" s="35" t="s">
+        <v>59</v>
+      </c>
+      <c r="J36" s="39" t="s">
         <v>91</v>
       </c>
-      <c r="G36" s="44" t="s">
-        <v>90</v>
-      </c>
-      <c r="H36" s="40" t="s">
+      <c r="K36" s="37" t="s">
+        <v>107</v>
+      </c>
+      <c r="L36" s="42" t="s">
         <v>105</v>
       </c>
-    </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="O36" s="43" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="37" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A37" s="8">
         <v>2</v>
       </c>
@@ -1643,17 +1877,23 @@
       <c r="D37" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="F37" s="38" t="s">
-        <v>19</v>
-      </c>
-      <c r="G37" s="44" t="s">
-        <v>93</v>
-      </c>
-      <c r="H37" s="40" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I37" s="35" t="s">
+        <v>43</v>
+      </c>
+      <c r="J37" s="39" t="s">
+        <v>84</v>
+      </c>
+      <c r="K37" s="37" t="s">
+        <v>97</v>
+      </c>
+      <c r="L37" s="42" t="s">
+        <v>105</v>
+      </c>
+      <c r="O37" s="43" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="38" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A38" s="8">
         <v>2</v>
       </c>
@@ -1666,17 +1906,23 @@
       <c r="D38" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="F38" s="38" t="s">
-        <v>20</v>
-      </c>
-      <c r="G38" s="44" t="s">
-        <v>92</v>
-      </c>
-      <c r="H38" s="40" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I38" s="35" t="s">
+        <v>29</v>
+      </c>
+      <c r="J38" s="39" t="s">
+        <v>93</v>
+      </c>
+      <c r="K38" s="37" t="s">
+        <v>102</v>
+      </c>
+      <c r="L38" s="42" t="s">
+        <v>105</v>
+      </c>
+      <c r="O38" s="44" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="39" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A39" s="8">
         <v>3</v>
       </c>
@@ -1689,17 +1935,20 @@
       <c r="D39" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="F39" s="38" t="s">
-        <v>21</v>
-      </c>
-      <c r="G39" s="44" t="s">
-        <v>84</v>
-      </c>
-      <c r="H39" s="40" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="40" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I39" s="36" t="s">
+        <v>58</v>
+      </c>
+      <c r="J39" s="40" t="s">
+        <v>92</v>
+      </c>
+      <c r="K39" s="38" t="s">
+        <v>106</v>
+      </c>
+      <c r="O39" s="43" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="40" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A40" s="11">
         <v>3</v>
       </c>
@@ -1712,22 +1961,13 @@
       <c r="D40" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="F40" s="39" t="s">
-        <v>29</v>
-      </c>
-      <c r="G40" s="46" t="s">
-        <v>94</v>
-      </c>
-      <c r="H40" s="41" t="s">
-        <v>106</v>
-      </c>
-      <c r="I40" s="37"/>
-    </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="I41" s="36"/>
-    </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="I42" s="36"/>
+      <c r="L40" s="34"/>
+      <c r="O40" s="43" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="41" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="I41" s="33"/>
     </row>
   </sheetData>
   <mergeCells count="1">
